--- a/04_DESIGN_TABLES/DesignTable_6404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6404_SW2.xlsx
@@ -1339,12 +1339,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1747 = 0.531 (table had 0.5) [user 2026-10-18 A19] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.827 from the End A tip)</t>
+          <t>A19 (user 2026-10-18, group 3 open): D1@BORE 0.5 -&gt; OMi 0.531 (Items!S1747, M069) | A11 (user 2026-10-18): OMi bore 0.531 wider than the -06 port drill 0.50 -&gt; capped at 0.50 (report to OMi) | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.827 from the End A tip)</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1464,12 +1464,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData) | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L32@DRIVE=1.5~1.500; C1HEX@HEX=1~1.000</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6404_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6404_SW2.xlsx
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="C2" t="n">
-        <v>0.61372</v>
+        <v>0.57735</v>
       </c>
       <c r="D2" t="n">
-        <v>1.063</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0.40779</v>
@@ -669,13 +669,13 @@
         <v>0.37383</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Z2" t="n">
         <v>0.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.962</v>
+        <v>1.002</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -709,12 +709,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1749 Overall Length = 1.650 (table had 1.69); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1749 Hex Flat = 1.063 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1749 Overall Length = 1.650 (table had 1.69); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1749 Hex Flat = 1.063 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.65) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.063) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Brennan 6404-08-08 STEP overall 1.650 vs Air-Way 1.65: close (difference 0.000, normal between manufacturers)</t>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.65 -&gt; Air-Way 1.69 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.063 -&gt; Air-Way 1 | Brennan 6404-08-08 STEP overall 1.650 vs Air-Way 1.69: close (difference 0.040, normal between manufacturers)</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="C3" t="n">
         <v>0.39837</v>
@@ -799,13 +799,13 @@
         <v>0.21706</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
         <v>0.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.513</v>
+        <v>0.583</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -839,7 +839,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1743 Overall Length = 1.060 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1743 Overall Length = 1.060 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.06) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.06 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -855,7 +860,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="C4" t="n">
         <v>0.39837</v>
@@ -924,13 +929,13 @@
         <v>0.21706</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
         <v>0.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.793</v>
+        <v>0.763</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -964,7 +969,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1744 Overall Length = 1.340 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1744 Overall Length = 1.340 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.31 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.34) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.34 -&gt; Air-Way 1.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -980,7 +990,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="C5" t="n">
         <v>0.50807</v>
@@ -1049,13 +1059,13 @@
         <v>0.28007</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
         <v>0.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.981</v>
+        <v>0.771</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1089,7 +1099,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1745 Overall Length = 1.590 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1745 Overall Length = 1.590 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.59) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.59 -&gt; Air-Way 1.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1108,10 +1123,10 @@
         <v>1.38</v>
       </c>
       <c r="C6" t="n">
-        <v>0.46939</v>
+        <v>0.50807</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="E6" t="n">
         <v>0.32823</v>
@@ -1214,7 +1229,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1746 Hex Flat = 0.813 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1746 Hex Flat = 0.813 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: Air-Way 0.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.813) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.813 -&gt; Air-Way 0.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1230,7 +1250,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.58</v>
+        <v>1.1</v>
       </c>
       <c r="C7" t="n">
         <v>0.50807</v>
@@ -1299,13 +1319,13 @@
         <v>0.28007</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
         <v>0.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.971</v>
+        <v>0.491</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1339,12 +1359,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1747 = 0.531 (table had 0.5) [user 2026-10-18 A19] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1747 = 0.531 (table had 0.5) [user 2026-10-18 A19]; L32@DRIVE: Air-Way 1.1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port; female ORB port DEEP BORE (2026-10-01): through-bore 0.5 &gt;= port minor 0.5 -&gt; port drilled through, NO 120deg drill point (ORBFB_DRILLANG 90): the minor bore ends flat at the measured port depth 0.609 and the through-bore carries on at the same diameter; thread length unchanged (= the measured port depth) (ASSUMPTION - the nine Brennan STEPs with a female ORB port, 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / -24-20-O, all have a through-bore SMALLER than the port minor, joined by the 120deg drill point; the Brennan TFA catalog p16 (6410-O, B DRILL) gives the through drill = the port minor on the short reducers, i.e. drilled through; no Brennan STEP of such a part yet)</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): D1@BORE 0.5 -&gt; OMi 0.531 (Items!S1747, M069) | A11 (user 2026-10-18): OMi bore 0.531 wider than the -06 port drill 0.50 -&gt; capped at 0.50 (report to OMi) | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.827 from the End A tip)</t>
+          <t>A19 (user 2026-10-18, group 3 open): D1@BORE 0.5 -&gt; OMi 0.531 (Items!S1747, M069) | A11 (user 2026-10-18): OMi bore 0.531 wider than the -06 port drill 0.50 -&gt; capped at 0.50 (report to OMi) | 2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.1 | DEEP BORE: through-bore 0.5 = port minor 0.5000 -&gt; port drilled through, no drill point (flat at the minor-bore bottom 0.609 from the port face; the 120deg point would have ended 0.753 deep, 0.347 from the End A tip); female port reaches 0.491 from the End A tip, inside the End A thread/groove zone (0.750); radial wall there min 0.086 at 0.491 from the tip (OK)</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1490,7 +1510,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="C9" t="n">
         <v>0.7216900000000001</v>
@@ -1559,13 +1579,13 @@
         <v>0.43866</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Z9" t="n">
         <v>0.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.969</v>
+        <v>1.029</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1599,7 +1619,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1751 Overall Length = 1.750 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1751 Overall Length = 1.750 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.75) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.75 -&gt; Air-Way 1.81</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1615,7 +1640,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="C10" t="n">
         <v>0.7216900000000001</v>
@@ -1684,13 +1709,13 @@
         <v>0.43866</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="Z10" t="n">
         <v>0.72</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.069</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -1724,7 +1749,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1752 Overall Length = 1.850 (table had 1.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1752 Overall Length = 1.850 (table had 1.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.85) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.85 -&gt; Air-Way 1.72</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1740,7 +1770,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="C11" t="n">
         <v>0.79674</v>
@@ -1809,13 +1839,13 @@
         <v>0.53011</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Z11" t="n">
         <v>0.53</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.054</v>
+        <v>1.064</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -1849,7 +1879,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1753 Overall Length = 1.960 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1753 Overall Length = 1.960 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.96) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.96 -&gt; Air-Way 1.97</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1865,7 +1900,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="C12" t="n">
         <v>0.79674</v>
@@ -1934,13 +1969,13 @@
         <v>0.53011</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Z12" t="n">
         <v>0.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.074</v>
+        <v>1.064</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -1974,7 +2009,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1754 Overall Length = 1.980 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1754 Overall Length = 1.980 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1990,7 +2030,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="C13" t="n">
         <v>0.94108</v>
@@ -2059,13 +2099,13 @@
         <v>0.65511</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Z13" t="n">
         <v>0.72</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.004</v>
+        <v>1.064</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2099,7 +2139,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1755 Overall Length = 1.910 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1755 Overall Length = 1.910 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.91) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.91 -&gt; Air-Way 1.97</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2115,7 +2160,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="C14" t="n">
         <v>0.94108</v>
@@ -2184,13 +2229,13 @@
         <v>0.65511</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Z14" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.194</v>
+        <v>1.254</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2224,7 +2269,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1756 Overall Length = 2.100 (table had 2.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1756 Overall Length = 2.100 (table had 2.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 2.16 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 2.1 -&gt; Air-Way 2.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2240,7 +2290,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="C15" t="n">
         <v>1.29904</v>
@@ -2309,13 +2359,13 @@
         <v>0.93511</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Z15" t="n">
         <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.324</v>
+        <v>1.394</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -2349,7 +2399,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1759 Overall Length = 2.230 (table had 2.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1759 Overall Length = 2.230 (table had 2.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 2.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female SAE ORB port: minor bore = Air-Way D3 (port drill); O-ring chamfer (12deg at -04/-06, 15deg from -08 up), 45deg lead-in, minor-bore depth and 120deg drill point measured per port size on the Brennan 6404-04/-06/-08/-10/-12/-16/-24 and 6410-12-08-O / 6410-24-20-O STEPs (-08 measured twice, agree; single manufacturer); straight helical UN thread over the port depth; hex over the full body length, end chamfers NOT modelled; male NPTF end per ASME B1.20.3 + the 5404 Brennan-measured end length (Brennan 6404-08-08: 0.75 = the 5404 value); bore D1 from the male tip to the port</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 2.23 -&gt; Air-Way 2.3</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
